--- a/output/SMT/DeepSeek-V3/violation feedback results/task_analysis_results_SMT_DeepSeek-V3_calendar_v2.xlsx
+++ b/output/SMT/DeepSeek-V3/violation feedback results/task_analysis_results_SMT_DeepSeek-V3_calendar_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laiqimei/Desktop/Academic/UPenn/CCB Lab/Project/calendar-planning/output/SMT/DeepSeek-V3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laiqimei/Desktop/Academic/UPenn/CCB Lab/Project/calendar-planning/output/SMT/DeepSeek-V3/violation feedback results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{08130989-C028-AC4E-BB7E-95E6FC3B09F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77878A02-826F-BD42-ACEB-9E4F568237A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2540" yWindow="2420" windowWidth="30240" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="6500" windowWidth="30240" windowHeight="17480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -22,9 +22,8 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="43" r:id="rId4"/>
+    <pivotCache cacheId="94" r:id="rId4"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1112,7 +1111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1121,8 +1120,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1575,7 +1573,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE603055-446D-3644-95B1-9D0984E8F4AF}" name="PivotTable8" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE603055-446D-3644-95B1-9D0984E8F4AF}" name="PivotTable8" cacheId="94" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -1935,7 +1933,7 @@
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>75</v>
       </c>
     </row>
@@ -1943,7 +1941,7 @@
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>12</v>
       </c>
     </row>
@@ -1951,7 +1949,7 @@
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>4</v>
       </c>
     </row>
@@ -1959,7 +1957,7 @@
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>2</v>
       </c>
     </row>
@@ -1967,7 +1965,7 @@
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>7</v>
       </c>
     </row>
@@ -1975,7 +1973,7 @@
       <c r="A9" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>100</v>
       </c>
     </row>
@@ -2830,11 +2828,11 @@
       <c r="G1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2857,7 +2855,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2932,7 +2930,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2955,7 +2953,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2978,7 +2976,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3001,7 +2999,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3024,7 +3022,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3174,7 +3172,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -3197,7 +3195,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -3324,7 +3322,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -3402,7 +3400,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -3477,7 +3475,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3500,7 +3498,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -3523,7 +3521,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -3624,7 +3622,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -3647,7 +3645,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -3670,7 +3668,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3693,7 +3691,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -3716,7 +3714,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -3739,7 +3737,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -3762,7 +3760,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -3785,7 +3783,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -3808,7 +3806,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3831,7 +3829,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -3854,7 +3852,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -3877,7 +3875,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -3926,7 +3924,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -3949,7 +3947,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -4076,7 +4074,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>31</v>
       </c>
@@ -4102,7 +4100,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>32</v>
       </c>
@@ -4125,7 +4123,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>33</v>
       </c>
@@ -4148,7 +4146,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>34</v>
       </c>
@@ -4197,7 +4195,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -4220,7 +4218,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>36</v>
       </c>
@@ -4243,7 +4241,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>37</v>
       </c>
@@ -4370,7 +4368,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>38</v>
       </c>
@@ -4396,7 +4394,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -4419,7 +4417,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -4442,7 +4440,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>41</v>
       </c>
@@ -4465,7 +4463,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>42</v>
       </c>
@@ -4488,7 +4486,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>43</v>
       </c>
@@ -4511,7 +4509,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>44</v>
       </c>
@@ -4534,7 +4532,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>45</v>
       </c>
@@ -4557,7 +4555,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>46</v>
       </c>
@@ -4580,7 +4578,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>47</v>
       </c>
@@ -4603,7 +4601,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -4652,7 +4650,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>49</v>
       </c>
@@ -4675,7 +4673,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>50</v>
       </c>
@@ -4698,7 +4696,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>51</v>
       </c>
@@ -4721,7 +4719,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -4848,7 +4846,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>53</v>
       </c>
@@ -4874,7 +4872,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>54</v>
       </c>
@@ -4897,7 +4895,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>55</v>
       </c>
@@ -4920,7 +4918,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>56</v>
       </c>
@@ -4943,7 +4941,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>57</v>
       </c>
@@ -4966,7 +4964,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>58</v>
       </c>
@@ -4989,7 +4987,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>59</v>
       </c>
@@ -5038,7 +5036,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>60</v>
       </c>
@@ -5087,7 +5085,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>61</v>
       </c>
@@ -5110,7 +5108,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>62</v>
       </c>
@@ -5133,7 +5131,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -5156,7 +5154,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>64</v>
       </c>
@@ -5231,7 +5229,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>65</v>
       </c>
@@ -5254,7 +5252,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -5277,7 +5275,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -5300,7 +5298,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>68</v>
       </c>
@@ -5323,7 +5321,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -5346,7 +5344,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>70</v>
       </c>
@@ -5369,7 +5367,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>71</v>
       </c>
@@ -5418,7 +5416,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>72</v>
       </c>
@@ -5441,7 +5439,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>73</v>
       </c>
@@ -5464,7 +5462,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>74</v>
       </c>
@@ -5487,7 +5485,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>75</v>
       </c>
@@ -5510,7 +5508,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>76</v>
       </c>
@@ -5533,7 +5531,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>77</v>
       </c>
@@ -5582,7 +5580,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>78</v>
       </c>
@@ -5631,7 +5629,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>79</v>
       </c>
@@ -5654,7 +5652,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>80</v>
       </c>
@@ -5781,7 +5779,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>81</v>
       </c>
@@ -5807,7 +5805,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>82</v>
       </c>
@@ -5830,7 +5828,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>83</v>
       </c>
@@ -5957,7 +5955,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>84</v>
       </c>
@@ -5983,7 +5981,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -6006,7 +6004,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>86</v>
       </c>
@@ -6107,7 +6105,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>87</v>
       </c>
@@ -6130,7 +6128,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>88</v>
       </c>
@@ -6153,7 +6151,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>89</v>
       </c>
@@ -6176,7 +6174,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>90</v>
       </c>
@@ -6199,7 +6197,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>91</v>
       </c>
@@ -6222,7 +6220,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>92</v>
       </c>
@@ -6271,7 +6269,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>93</v>
       </c>
@@ -6294,7 +6292,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>94</v>
       </c>
@@ -6343,7 +6341,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>95</v>
       </c>
@@ -6392,7 +6390,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>96</v>
       </c>
@@ -6415,7 +6413,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>97</v>
       </c>
@@ -6438,7 +6436,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>98</v>
       </c>
@@ -6461,7 +6459,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>99</v>
       </c>
@@ -6510,7 +6508,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>100</v>
       </c>
@@ -6533,7 +6531,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>101</v>
       </c>
@@ -6558,9 +6556,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H155" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="5">
       <filters>
-        <filter val="5"/>
+        <filter val="TRUE"/>
       </filters>
     </filterColumn>
   </autoFilter>
